--- a/游戏设计王/老虎机数学专题-黏性百搭.xlsx
+++ b/游戏设计王/老虎机数学专题-黏性百搭.xlsx
@@ -460,13 +460,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
     <numFmt numFmtId="177" formatCode="0.00000000"/>
+    <numFmt numFmtId="178" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1172,7 +1173,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1217,6 +1218,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -7373,11 +7378,11 @@
         <f>B22</f>
         <v>1</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="38">
         <f>C39/B39</f>
         <v>0.0625</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="39">
         <f>1-D39</f>
         <v>0.9375</v>
       </c>
@@ -7409,11 +7414,11 @@
         <f>C22</f>
         <v>1</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="38">
         <f>C40/B40</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="39">
         <f>1-D40</f>
         <v>0.933333333333333</v>
       </c>
@@ -7445,11 +7450,11 @@
         <f>D22</f>
         <v>1</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="38">
         <f>C41/B41</f>
         <v>0.0714285714285714</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="39">
         <f>1-D41</f>
         <v>0.928571428571429</v>
       </c>
@@ -7481,11 +7486,11 @@
         <f>E22</f>
         <v>1</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="38">
         <f>C42/B42</f>
         <v>0.0769230769230769</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="39">
         <f>1-D42</f>
         <v>0.923076923076923</v>
       </c>
@@ -7517,11 +7522,11 @@
         <f>F22</f>
         <v>1</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="38">
         <f>C43/B43</f>
         <v>0.0833333333333333</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="39">
         <f>1-D43</f>
         <v>0.916666666666667</v>
       </c>
@@ -7700,7 +7705,7 @@
       <c r="F50" s="4">
         <v>0</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="39">
         <f t="shared" ref="G50:G81" si="0">(((B$28+B50*B$33)*(C$28+C50*C$33)*(D$28+D50*D$33)*(E$21-(E$28+E50*E$33))*(F$21-(F$28+F50*F$33)))*B$87+((B$28+B50*B$33)*(C$28+C50*C$33)*(D$28+D50*D$33)*(E$28+E50*E$33)*(F$21-(F$28+F50*F$33)))*C$87+((B$28+B50*B$33)*(C$28+C50*C$33)*(D$28+D50*D$33)*(E$28+E50*E$33)*(F$28+F50*F$33))*D$87+((B$29+B50*B$33)*(C$29+C50*C$33)*(D$29+D50*D$33)*(E$21-(E$29+E50*E$33))*(F$21-(F$29+F50*F$33)))*B$88+((B$29+B50*B$33)*(C$29+C50*C$33)*(D$29+D50*D$33)*(E$29+E50*E$33)*(F$21-(F$29+F50*F$33)))*C$88+((B$29+B50*B$33)*(C$29+C50*C$33)*(D$29+D50*D$33)*(E$29+E50*E$33)*(F$29+F50*F$33))*D$88+((B$30+B50*B$33)*(C$30+C50*C$33)*(D$30+D50*D$33)*(E$21-(E$30+E50*E$33))*(F$21-(F$30+F50*F$33)))*B$89+((B$30+B50*B$33)*(C$30+C50*C$33)*(D$30+D50*D$33)*(E$30+E50*E$33)*(F$21-(F$30+F50*F$33)))*C$89+((B$30+B50*B$33)*(C$30+C50*C$33)*(D$30+D50*D$33)*(E$30+E50*E$33)*(F$30+F50*F$33))*D$89+((B$31+B50*B$33)*(C$31+C50*C$33)*(D$31+D50*D$33)*(E$21-(E$31+E50*E$33))*(F$21-(F$31+F50*F$33)))*B$90+((B$31+B50*B$33)*(C$31+C50*C$33)*(D$31+D50*D$33)*(E$31+E50*E$33)*(F$21-(F$31+F50*F$33)))*C$90+((B$31+B50*B$33)*(C$31+C50*C$33)*(D$31+D50*D$33)*(E$31+E50*E$33)*(F$31+F50*F$33))*D$90+((B$32+B50*B$33)*(C$32+C50*C$33)*(D$32+D50*D$33)*(E$21-(E$32+E50*E$33))*(F$21-(F$32+F50*F$33)))*B$91+((B$32+B50*B$33)*(C$32+C50*C$33)*(D$32+D50*D$33)*(E$32+E50*E$33)*(F$21-(F$32+F50*F$33)))*C$91+((B$32+B50*B$33)*(C$32+C50*C$33)*(D$32+D50*D$33)*(E$32+E50*E$33)*(F$32+F50*F$33))*D$91)/PRODUCT($B$21:$F$21)</f>
         <v>0.4907471001221</v>
       </c>
@@ -7735,7 +7740,7 @@
       <c r="F51" s="4">
         <v>1</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="39">
         <f t="shared" si="0"/>
         <v>0.531364468864469</v>
       </c>
@@ -7770,7 +7775,7 @@
       <c r="F52" s="4">
         <v>0</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="39">
         <f t="shared" si="0"/>
         <v>0.592653006715507</v>
       </c>
@@ -7805,7 +7810,7 @@
       <c r="F53" s="4">
         <v>1</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="39">
         <f t="shared" si="0"/>
         <v>0.65090811965812</v>
       </c>
@@ -7840,7 +7845,7 @@
       <c r="F54" s="4">
         <v>0</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="39">
         <f t="shared" si="0"/>
         <v>0.641111492673993</v>
       </c>
@@ -7875,7 +7880,7 @@
       <c r="F55" s="4">
         <v>1</v>
       </c>
-      <c r="G55" s="11">
+      <c r="G55" s="39">
         <f t="shared" si="0"/>
         <v>0.692880036630037</v>
       </c>
@@ -7910,7 +7915,7 @@
       <c r="F56" s="4">
         <v>0</v>
       </c>
-      <c r="G56" s="11">
+      <c r="G56" s="39">
         <f t="shared" si="0"/>
         <v>0.774811126373626</v>
       </c>
@@ -7945,7 +7950,7 @@
       <c r="F57" s="4">
         <v>1</v>
       </c>
-      <c r="G57" s="11">
+      <c r="G57" s="39">
         <f t="shared" si="0"/>
         <v>0.849950396825397</v>
       </c>
@@ -7980,7 +7985,7 @@
       <c r="F58" s="4">
         <v>0</v>
       </c>
-      <c r="G58" s="11">
+      <c r="G58" s="39">
         <f t="shared" si="0"/>
         <v>0.635645604395604</v>
       </c>
@@ -8015,7 +8020,7 @@
       <c r="F59" s="4">
         <v>1</v>
       </c>
-      <c r="G59" s="11">
+      <c r="G59" s="39">
         <f t="shared" si="0"/>
         <v>0.687442765567766</v>
       </c>
@@ -8050,7 +8055,7 @@
       <c r="F60" s="4">
         <v>0</v>
       </c>
-      <c r="G60" s="11">
+      <c r="G60" s="39">
         <f t="shared" si="0"/>
         <v>0.767971611721612</v>
       </c>
@@ -8085,7 +8090,7 @@
       <c r="F61" s="4">
         <v>1</v>
       </c>
-      <c r="G61" s="11">
+      <c r="G61" s="39">
         <f t="shared" si="0"/>
         <v>0.842796092796093</v>
       </c>
@@ -8120,7 +8125,7 @@
       <c r="F62" s="4">
         <v>0</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G62" s="39">
         <f t="shared" si="0"/>
         <v>0.83316163003663</v>
       </c>
@@ -8155,7 +8160,7 @@
       <c r="F63" s="4">
         <v>1</v>
       </c>
-      <c r="G63" s="11">
+      <c r="G63" s="39">
         <f t="shared" si="0"/>
         <v>0.899296016483517</v>
       </c>
@@ -8190,7 +8195,7 @@
       <c r="F64" s="4">
         <v>0</v>
       </c>
-      <c r="G64" s="11">
+      <c r="G64" s="39">
         <f t="shared" si="0"/>
         <v>1.00732600732601</v>
       </c>
@@ -8225,7 +8230,7 @@
       <c r="F65" s="4">
         <v>1</v>
       </c>
-      <c r="G65" s="11">
+      <c r="G65" s="39">
         <f t="shared" si="0"/>
         <v>1.10409035409035</v>
       </c>
@@ -8260,7 +8265,7 @@
       <c r="F66" s="4">
         <v>0</v>
       </c>
-      <c r="G66" s="11">
+      <c r="G66" s="39">
         <f t="shared" si="0"/>
         <v>0.632020757020757</v>
       </c>
@@ -8295,7 +8300,7 @@
       <c r="F67" s="4">
         <v>1</v>
       </c>
-      <c r="G67" s="11">
+      <c r="G67" s="39">
         <f t="shared" si="0"/>
         <v>0.683722527472527</v>
       </c>
@@ -8330,7 +8335,7 @@
       <c r="F68" s="4">
         <v>0</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G68" s="39">
         <f t="shared" si="0"/>
         <v>0.76377442002442</v>
       </c>
@@ -8365,7 +8370,7 @@
       <c r="F69" s="4">
         <v>1</v>
       </c>
-      <c r="G69" s="11">
+      <c r="G69" s="39">
         <f t="shared" si="0"/>
         <v>0.838331807081807</v>
       </c>
@@ -8400,7 +8405,7 @@
       <c r="F70" s="4">
         <v>0</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G70" s="39">
         <f t="shared" si="0"/>
         <v>0.827724358974359</v>
       </c>
@@ -8435,7 +8440,7 @@
       <c r="F71" s="4">
         <v>1</v>
       </c>
-      <c r="G71" s="11">
+      <c r="G71" s="39">
         <f t="shared" si="0"/>
         <v>0.893715659340659</v>
       </c>
@@ -8470,7 +8475,7 @@
       <c r="F72" s="4">
         <v>0</v>
       </c>
-      <c r="G72" s="11">
+      <c r="G72" s="39">
         <f t="shared" si="0"/>
         <v>1.00103021978022</v>
       </c>
@@ -8505,7 +8510,7 @@
       <c r="F73" s="4">
         <v>1</v>
       </c>
-      <c r="G73" s="11">
+      <c r="G73" s="39">
         <f t="shared" si="0"/>
         <v>1.09739392551893</v>
       </c>
@@ -8540,7 +8545,7 @@
       <c r="F74" s="4">
         <v>0</v>
       </c>
-      <c r="G74" s="11">
+      <c r="G74" s="39">
         <f t="shared" si="0"/>
         <v>0.820436507936508</v>
       </c>
@@ -8575,7 +8580,7 @@
       <c r="F75" s="4">
         <v>1</v>
       </c>
-      <c r="G75" s="11">
+      <c r="G75" s="39">
         <f t="shared" si="0"/>
         <v>0.886465964590965</v>
       </c>
@@ -8610,7 +8615,7 @@
       <c r="F76" s="4">
         <v>0</v>
       </c>
-      <c r="G76" s="11">
+      <c r="G76" s="39">
         <f t="shared" si="0"/>
         <v>0.991910866910867</v>
       </c>
@@ -8645,7 +8650,7 @@
       <c r="F77" s="4">
         <v>1</v>
       </c>
-      <c r="G77" s="11">
+      <c r="G77" s="39">
         <f t="shared" si="0"/>
         <v>1.08785485347985</v>
       </c>
@@ -8680,7 +8685,7 @@
       <c r="F78" s="4">
         <v>0</v>
       </c>
-      <c r="G78" s="11">
+      <c r="G78" s="39">
         <f t="shared" si="0"/>
         <v>1.07821085164835</v>
       </c>
@@ -8715,7 +8720,7 @@
       <c r="F79" s="4">
         <v>1</v>
       </c>
-      <c r="G79" s="11">
+      <c r="G79" s="39">
         <f t="shared" si="0"/>
         <v>1.16265071733822</v>
       </c>
@@ -8750,7 +8755,7 @@
       <c r="F80" s="4">
         <v>0</v>
       </c>
-      <c r="G80" s="11">
+      <c r="G80" s="39">
         <f t="shared" si="0"/>
         <v>1.3045157967033</v>
       </c>
@@ -8785,7 +8790,7 @@
       <c r="F81" s="4">
         <v>1</v>
       </c>
-      <c r="G81" s="11">
+      <c r="G81" s="39">
         <f t="shared" si="0"/>
         <v>1.42886713980464</v>
       </c>
@@ -11343,7 +11348,7 @@
       <c r="A135" s="4">
         <v>1</v>
       </c>
-      <c r="B135" s="11">
+      <c r="B135" s="39">
         <f>SUMPRODUCT(G97:G128,$G$50:$G$81)</f>
         <v>0.4907471001221</v>
       </c>
@@ -11368,7 +11373,7 @@
       <c r="A136" s="4">
         <v>2</v>
       </c>
-      <c r="B136" s="11">
+      <c r="B136" s="39">
         <f>SUMPRODUCT(H97:H128,$G$50:$G$81)</f>
         <v>0.532607591174602</v>
       </c>
@@ -11393,7 +11398,7 @@
       <c r="A137" s="4">
         <v>3</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B137" s="39">
         <f>SUMPRODUCT(I97:I128,$G$50:$G$81)</f>
         <v>0.574130698287933</v>
       </c>
@@ -11418,7 +11423,7 @@
       <c r="A138" s="4">
         <v>4</v>
       </c>
-      <c r="B138" s="11">
+      <c r="B138" s="39">
         <f>SUMPRODUCT(J97:J128,$G$50:$G$81)</f>
         <v>0.615097310362884</v>
       </c>
@@ -11443,7 +11448,7 @@
       <c r="A139" s="4">
         <v>5</v>
       </c>
-      <c r="B139" s="11">
+      <c r="B139" s="39">
         <f>SUMPRODUCT(K97:K128,$G$50:$G$81)</f>
         <v>0.655317663763883</v>
       </c>
@@ -11468,7 +11473,7 @@
       <c r="A140" s="4">
         <v>6</v>
       </c>
-      <c r="B140" s="11">
+      <c r="B140" s="39">
         <f>SUMPRODUCT(L97:L128,$G$50:$G$81)</f>
         <v>0.694630480655415</v>
       </c>
@@ -11493,7 +11498,7 @@
       <c r="A141" s="4">
         <v>7</v>
       </c>
-      <c r="B141" s="11">
+      <c r="B141" s="39">
         <f>SUMPRODUCT(M97:M128,$G$50:$G$81)</f>
         <v>0.732901562314913</v>
       </c>
@@ -11518,7 +11523,7 @@
       <c r="A142" s="4">
         <v>8</v>
       </c>
-      <c r="B142" s="11">
+      <c r="B142" s="39">
         <f>SUMPRODUCT(N97:N128,$G$50:$G$81)</f>
         <v>0.770022003325889</v>
       </c>
@@ -11543,7 +11548,7 @@
       <c r="A143" s="4">
         <v>9</v>
       </c>
-      <c r="B143" s="11">
+      <c r="B143" s="39">
         <f>SUMPRODUCT(O97:O128,$G$50:$G$81)</f>
         <v>0.805906164620519</v>
       </c>
@@ -11568,7 +11573,7 @@
       <c r="A144" s="4">
         <v>10</v>
       </c>
-      <c r="B144" s="11">
+      <c r="B144" s="39">
         <f>SUMPRODUCT(P97:P128,$G$50:$G$81)</f>
         <v>0.84048951712279</v>
       </c>
@@ -11613,7 +11618,7 @@
       <c r="A146" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B146" s="16">
+      <c r="B146" s="41">
         <f>SUM(B135:B144)</f>
         <v>6.71185009175093</v>
       </c>
